--- a/outputs/438-18.xlsx
+++ b/outputs/438-18.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
   <si>
     <t xml:space="preserve">ITEM</t>
   </si>
@@ -103,6 +103,21 @@
   </si>
   <si>
     <t xml:space="preserve">ITALY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT</t>
   </si>
 </sst>
 </file>
@@ -205,27 +220,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -425,7 +440,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="28.42"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -445,7 +460,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
@@ -465,7 +480,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
@@ -485,7 +500,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
@@ -505,7 +520,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
@@ -525,7 +540,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
@@ -567,7 +582,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="28"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -581,94 +596,74 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="n">
-        <f aca="false">INPUT!A2</f>
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="str">
-        <f aca="false">INPUT!C2</f>
-        <v>CARS-12</v>
-      </c>
-      <c r="C2" s="6" t="str">
-        <f aca="false">INPUT!E2</f>
-        <v>GMC</v>
-      </c>
-      <c r="D2" s="6" t="str">
-        <f aca="false">IF(INPUT!F2="UNATIDE STATES AMERICAN","USA",IF(INPUT!F2="FRANCE","FRA",IF(INPUT!F2="KOREA","KOR",IF(INPUT!F2="GERMANY","GR",IF(INPUT!F2="ITALY","IT","")))))</f>
-        <v>USA</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="n">
-        <f aca="false">INPUT!A3</f>
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="str">
-        <f aca="false">INPUT!C3</f>
-        <v>CARS-13</v>
-      </c>
-      <c r="C3" s="6" t="str">
-        <f aca="false">INPUT!E3</f>
-        <v>PEGUE</v>
-      </c>
-      <c r="D3" s="6" t="str">
-        <f aca="false">IF(INPUT!F3="UNATIDE STATES AMERICAN","USA",IF(INPUT!F3="FRANCE","FRA",IF(INPUT!F3="KOREA","KOR",IF(INPUT!F3="GERMANY","GR",IF(INPUT!F3="ITALY","IT","")))))</f>
-        <v>FRA</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="n">
-        <f aca="false">INPUT!A4</f>
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="str">
-        <f aca="false">INPUT!C4</f>
-        <v>CARS-14</v>
-      </c>
-      <c r="C4" s="6" t="str">
-        <f aca="false">INPUT!E4</f>
-        <v>HUNDAY</v>
-      </c>
-      <c r="D4" s="6" t="str">
-        <f aca="false">IF(INPUT!F4="UNATIDE STATES AMERICAN","USA",IF(INPUT!F4="FRANCE","FRA",IF(INPUT!F4="KOREA","KOR",IF(INPUT!F4="GERMANY","GR",IF(INPUT!F4="ITALY","IT","")))))</f>
-        <v>KOR</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="n">
-        <f aca="false">INPUT!A5</f>
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="str">
-        <f aca="false">INPUT!C5</f>
-        <v>CARS-15</v>
-      </c>
-      <c r="C5" s="6" t="str">
-        <f aca="false">INPUT!E5</f>
-        <v>BMW</v>
-      </c>
-      <c r="D5" s="6" t="str">
-        <f aca="false">IF(INPUT!F5="UNATIDE STATES AMERICAN","USA",IF(INPUT!F5="FRANCE","FRA",IF(INPUT!F5="KOREA","KOR",IF(INPUT!F5="GERMANY","GR",IF(INPUT!F5="ITALY","IT","")))))</f>
-        <v>GR</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="n">
-        <f aca="false">INPUT!A6</f>
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="str">
-        <f aca="false">INPUT!C6</f>
-        <v>CARS-16</v>
-      </c>
-      <c r="C6" s="6" t="str">
-        <f aca="false">INPUT!E6</f>
-        <v>FIA</v>
-      </c>
-      <c r="D6" s="6" t="str">
-        <f aca="false">IF(INPUT!F6="UNATIDE STATES AMERICAN","USA",IF(INPUT!F6="FRANCE","FRA",IF(INPUT!F6="KOREA","KOR",IF(INPUT!F6="GERMANY","GR",IF(INPUT!F6="ITALY","IT","")))))</f>
-        <v>IT</v>
+      <c r="B6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/438-18.xlsx
+++ b/outputs/438-18.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t xml:space="preserve">ITEM</t>
   </si>
@@ -625,43 +625,25 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>16</v>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
       <c r="D4" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
       <c r="D5" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>24</v>
-      </c>
+      <c r="A6" s="3"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
       <c r="D6" s="6" t="s">
         <v>30</v>
       </c>
